--- a/РАБОЧИЙ СТОЛ/расчеты Останкино ЗПФ/проблемы.xlsx
+++ b/РАБОЧИЙ СТОЛ/расчеты Останкино ЗПФ/проблемы.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="22527"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\РАБОЧИЙ СТОЛ\расчеты Останкино ЗПФ\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Father\Work\2025_05\РАБОЧИЙ СТОЛ\расчеты Останкино ЗПФ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E155C06C-DF45-43E2-9BE9-E72B4529E33B}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD4F5183-E9D4-47AB-B502-387081135EF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="16">
   <si>
     <t>Бердянск</t>
   </si>
@@ -67,6 +67,12 @@
   </si>
   <si>
     <t>6819 БЛИНЧ.КРУГЛЫЕ С САД.ЯБЛОК. пл. 1/300 зам. ОСТАНКИНО</t>
+  </si>
+  <si>
+    <t>Донецк</t>
+  </si>
+  <si>
+    <t>Мелитополь</t>
   </si>
 </sst>
 </file>
@@ -424,7 +430,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F18"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="61.42578125" bestFit="1" customWidth="1"/>
@@ -544,6 +550,136 @@
         <v>103</v>
       </c>
     </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C11" s="2">
+        <v>60</v>
+      </c>
+      <c r="D11" s="2"/>
+      <c r="E11" s="2"/>
+      <c r="F11" s="2">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C12" s="2">
+        <v>109.636</v>
+      </c>
+      <c r="D12" s="2"/>
+      <c r="E12" s="2"/>
+      <c r="F12" s="2">
+        <v>109.636</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C13" s="2">
+        <v>130</v>
+      </c>
+      <c r="D13" s="2"/>
+      <c r="E13" s="2"/>
+      <c r="F13" s="2">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C17" s="2">
+        <v>196.68199999999999</v>
+      </c>
+      <c r="D17" s="2"/>
+      <c r="E17" s="2"/>
+      <c r="F17" s="2">
+        <v>196.68199999999999</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C18" s="2">
+        <v>95.147999999999996</v>
+      </c>
+      <c r="D18" s="2"/>
+      <c r="E18" s="2"/>
+      <c r="F18" s="2">
+        <v>95.147999999999996</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
